--- a/research/traditional_assets/database/data/hungary/hungary_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/hungary/hungary_insurance_life.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.14</v>
+        <v>0.0241</v>
       </c>
       <c r="E2">
-        <v>0.0331</v>
+        <v>-0.0765</v>
       </c>
       <c r="G2">
-        <v>0.01952662721893491</v>
+        <v>0.08735332464146023</v>
       </c>
       <c r="H2">
-        <v>0.01952662721893491</v>
+        <v>0.08735332464146023</v>
       </c>
       <c r="I2">
-        <v>0.03279797125950972</v>
+        <v>0.05880052151238591</v>
       </c>
       <c r="J2">
-        <v>0.02560249797298463</v>
+        <v>0.05509262980289899</v>
       </c>
       <c r="K2">
-        <v>2.3</v>
+        <v>3.96</v>
       </c>
       <c r="L2">
-        <v>0.01944209636517329</v>
+        <v>0.05162972620599739</v>
       </c>
       <c r="M2">
-        <v>0.103</v>
+        <v>3.94</v>
       </c>
       <c r="N2">
-        <v>0.0009229390681003584</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="O2">
-        <v>0.04478260869565218</v>
+        <v>0.9949494949494949</v>
       </c>
       <c r="P2">
+        <v>3.94</v>
+      </c>
+      <c r="Q2">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="R2">
+        <v>0.9949494949494949</v>
+      </c>
+      <c r="S2">
         <v>0</v>
       </c>
-      <c r="Q2">
+      <c r="T2">
         <v>0</v>
       </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>0.103</v>
-      </c>
-      <c r="T2">
-        <v>1</v>
-      </c>
       <c r="U2">
-        <v>4.83</v>
+        <v>11.1</v>
       </c>
       <c r="V2">
-        <v>0.04327956989247312</v>
+        <v>0.1878172588832487</v>
       </c>
       <c r="W2">
-        <v>0.05311778290993072</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="X2">
-        <v>0.07450417856651685</v>
+        <v>0.1141091819445309</v>
       </c>
       <c r="Y2">
-        <v>-0.02138639565658614</v>
+        <v>-0.02610918194453091</v>
       </c>
       <c r="Z2">
-        <v>2.94667098413331</v>
+        <v>1.838006230529595</v>
       </c>
       <c r="AA2">
-        <v>0.07544213789832568</v>
+        <v>0.1012605968339888</v>
       </c>
       <c r="AB2">
-        <v>0.07403107715666418</v>
+        <v>0.1132675289537689</v>
       </c>
       <c r="AC2">
-        <v>0.001411060741661502</v>
+        <v>-0.01200693211978014</v>
       </c>
       <c r="AD2">
-        <v>1.56</v>
+        <v>1.29</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.56</v>
+        <v>1.29</v>
       </c>
       <c r="AG2">
-        <v>-3.27</v>
+        <v>-9.809999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.01378579003181336</v>
+        <v>0.02136115250869349</v>
       </c>
       <c r="AI2">
-        <v>0.03350515463917526</v>
+        <v>0.06865353911655137</v>
       </c>
       <c r="AJ2">
-        <v>-0.03018554417058986</v>
+        <v>-0.1990261716372489</v>
       </c>
       <c r="AK2">
-        <v>-0.07836089144500361</v>
+        <v>-1.275682704811443</v>
       </c>
       <c r="AL2">
-        <v>0.029</v>
+        <v>0.03</v>
       </c>
       <c r="AM2">
-        <v>0.029</v>
+        <v>0.03</v>
       </c>
       <c r="AN2">
-        <v>0.3263598326359833</v>
+        <v>0.2447817836812144</v>
       </c>
       <c r="AO2">
-        <v>133.7931034482758</v>
+        <v>150.3333333333333</v>
       </c>
       <c r="AP2">
-        <v>-0.6841004184100418</v>
+        <v>-1.861480075901328</v>
       </c>
       <c r="AQ2">
-        <v>133.7931034482758</v>
+        <v>150.3333333333333</v>
       </c>
     </row>
     <row r="3">
@@ -722,121 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.14</v>
+        <v>0.0241</v>
       </c>
       <c r="E3">
-        <v>0.0331</v>
+        <v>-0.0765</v>
       </c>
       <c r="G3">
-        <v>0.01952662721893491</v>
+        <v>0.08735332464146023</v>
       </c>
       <c r="H3">
-        <v>0.01952662721893491</v>
+        <v>0.08735332464146023</v>
       </c>
       <c r="I3">
-        <v>0.03279797125950972</v>
+        <v>0.05880052151238591</v>
       </c>
       <c r="J3">
-        <v>0.02560249797298463</v>
+        <v>0.05509262980289899</v>
       </c>
       <c r="K3">
-        <v>2.3</v>
+        <v>3.96</v>
       </c>
       <c r="L3">
-        <v>0.01944209636517329</v>
+        <v>0.05162972620599739</v>
       </c>
       <c r="M3">
-        <v>0.103</v>
+        <v>3.94</v>
       </c>
       <c r="N3">
-        <v>0.0009229390681003584</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="O3">
-        <v>0.04478260869565218</v>
+        <v>0.9949494949494949</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>3.94</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.9949494949494949</v>
       </c>
       <c r="S3">
-        <v>0.103</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>4.83</v>
+        <v>11.1</v>
       </c>
       <c r="V3">
-        <v>0.04327956989247312</v>
+        <v>0.1878172588832487</v>
       </c>
       <c r="W3">
-        <v>0.05311778290993072</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="X3">
-        <v>0.07450417856651685</v>
+        <v>0.1141091819445309</v>
       </c>
       <c r="Y3">
-        <v>-0.02138639565658614</v>
+        <v>-0.02610918194453091</v>
       </c>
       <c r="Z3">
-        <v>2.94667098413331</v>
+        <v>1.838006230529595</v>
       </c>
       <c r="AA3">
-        <v>0.07544213789832568</v>
+        <v>0.1012605968339888</v>
       </c>
       <c r="AB3">
-        <v>0.07403107715666418</v>
+        <v>0.1132675289537689</v>
       </c>
       <c r="AC3">
-        <v>0.001411060741661502</v>
+        <v>-0.01200693211978014</v>
       </c>
       <c r="AD3">
-        <v>1.56</v>
+        <v>1.29</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.56</v>
+        <v>1.29</v>
       </c>
       <c r="AG3">
-        <v>-3.27</v>
+        <v>-9.809999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.01378579003181336</v>
+        <v>0.02136115250869349</v>
       </c>
       <c r="AI3">
-        <v>0.03350515463917526</v>
+        <v>0.06865353911655137</v>
       </c>
       <c r="AJ3">
-        <v>-0.03018554417058986</v>
+        <v>-0.1990261716372489</v>
       </c>
       <c r="AK3">
-        <v>-0.07836089144500361</v>
+        <v>-1.275682704811443</v>
       </c>
       <c r="AL3">
-        <v>0.029</v>
+        <v>0.03</v>
       </c>
       <c r="AM3">
-        <v>0.029</v>
+        <v>0.03</v>
       </c>
       <c r="AN3">
-        <v>0.3263598326359833</v>
+        <v>0.2447817836812144</v>
       </c>
       <c r="AO3">
-        <v>133.7931034482758</v>
+        <v>150.3333333333333</v>
       </c>
       <c r="AP3">
-        <v>-0.6841004184100418</v>
+        <v>-1.861480075901328</v>
       </c>
       <c r="AQ3">
-        <v>133.7931034482758</v>
+        <v>150.3333333333333</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/hungary/hungary_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/hungary/hungary_insurance_life.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0241</v>
+        <v>0.07150000000000001</v>
       </c>
       <c r="E2">
-        <v>-0.0765</v>
+        <v>0.00959</v>
       </c>
       <c r="G2">
-        <v>0.08735332464146023</v>
+        <v>0.05205338809034907</v>
       </c>
       <c r="H2">
-        <v>0.08735332464146023</v>
+        <v>0.05205338809034907</v>
       </c>
       <c r="I2">
-        <v>0.05880052151238591</v>
+        <v>0.08121149897330596</v>
       </c>
       <c r="J2">
-        <v>0.05509262980289899</v>
+        <v>0.06150660511302274</v>
       </c>
       <c r="K2">
-        <v>3.96</v>
+        <v>5.4</v>
       </c>
       <c r="L2">
-        <v>0.05162972620599739</v>
+        <v>0.05544147843942505</v>
       </c>
       <c r="M2">
-        <v>3.94</v>
+        <v>4.62</v>
       </c>
       <c r="N2">
-        <v>0.06666666666666667</v>
+        <v>0.05789473684210527</v>
       </c>
       <c r="O2">
-        <v>0.9949494949494949</v>
+        <v>0.8555555555555555</v>
       </c>
       <c r="P2">
-        <v>3.94</v>
+        <v>4.62</v>
       </c>
       <c r="Q2">
-        <v>0.06666666666666667</v>
+        <v>0.05789473684210527</v>
       </c>
       <c r="R2">
-        <v>0.9949494949494949</v>
+        <v>0.8555555555555555</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>11.1</v>
+        <v>8.6</v>
       </c>
       <c r="V2">
-        <v>0.1878172588832487</v>
+        <v>0.1077694235588972</v>
       </c>
       <c r="W2">
-        <v>0.08799999999999999</v>
+        <v>0.3085714285714286</v>
       </c>
       <c r="X2">
-        <v>0.1141091819445309</v>
+        <v>0.09692740985282819</v>
       </c>
       <c r="Y2">
-        <v>-0.02610918194453091</v>
+        <v>0.2116440187186004</v>
       </c>
       <c r="Z2">
-        <v>1.838006230529595</v>
+        <v>12.66579973992198</v>
       </c>
       <c r="AA2">
-        <v>0.1012605968339888</v>
+        <v>0.7790303430440072</v>
       </c>
       <c r="AB2">
-        <v>0.1132675289537689</v>
+        <v>0.09647778500188005</v>
       </c>
       <c r="AC2">
-        <v>-0.01200693211978014</v>
+        <v>0.6825525580421271</v>
       </c>
       <c r="AD2">
-        <v>1.29</v>
+        <v>0.98</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.29</v>
+        <v>0.98</v>
       </c>
       <c r="AG2">
-        <v>-9.809999999999999</v>
+        <v>-7.619999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.02136115250869349</v>
+        <v>0.0121317157712305</v>
       </c>
       <c r="AI2">
-        <v>0.06865353911655137</v>
+        <v>0.0168732782369146</v>
       </c>
       <c r="AJ2">
-        <v>-0.1990261716372489</v>
+        <v>-0.1055694098088113</v>
       </c>
       <c r="AK2">
-        <v>-1.275682704811443</v>
+        <v>-0.1540016168148747</v>
       </c>
       <c r="AL2">
-        <v>0.03</v>
+        <v>0.043</v>
       </c>
       <c r="AM2">
-        <v>0.03</v>
+        <v>0.043</v>
       </c>
       <c r="AN2">
-        <v>0.2447817836812144</v>
+        <v>0.1121281464530892</v>
       </c>
       <c r="AO2">
-        <v>150.3333333333333</v>
+        <v>183.953488372093</v>
       </c>
       <c r="AP2">
-        <v>-1.861480075901328</v>
+        <v>-0.871853546910755</v>
       </c>
       <c r="AQ2">
-        <v>150.3333333333333</v>
+        <v>183.953488372093</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0241</v>
+        <v>0.07150000000000001</v>
       </c>
       <c r="E3">
-        <v>-0.0765</v>
+        <v>0.00959</v>
       </c>
       <c r="G3">
-        <v>0.08735332464146023</v>
+        <v>0.05205338809034907</v>
       </c>
       <c r="H3">
-        <v>0.08735332464146023</v>
+        <v>0.05205338809034907</v>
       </c>
       <c r="I3">
-        <v>0.05880052151238591</v>
+        <v>0.08121149897330596</v>
       </c>
       <c r="J3">
-        <v>0.05509262980289899</v>
+        <v>0.06150660511302274</v>
       </c>
       <c r="K3">
-        <v>3.96</v>
+        <v>5.4</v>
       </c>
       <c r="L3">
-        <v>0.05162972620599739</v>
+        <v>0.05544147843942505</v>
       </c>
       <c r="M3">
-        <v>3.94</v>
+        <v>4.62</v>
       </c>
       <c r="N3">
-        <v>0.06666666666666667</v>
+        <v>0.05789473684210527</v>
       </c>
       <c r="O3">
-        <v>0.9949494949494949</v>
+        <v>0.8555555555555555</v>
       </c>
       <c r="P3">
-        <v>3.94</v>
+        <v>4.62</v>
       </c>
       <c r="Q3">
-        <v>0.06666666666666667</v>
+        <v>0.05789473684210527</v>
       </c>
       <c r="R3">
-        <v>0.9949494949494949</v>
+        <v>0.8555555555555555</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>11.1</v>
+        <v>8.6</v>
       </c>
       <c r="V3">
-        <v>0.1878172588832487</v>
+        <v>0.1077694235588972</v>
       </c>
       <c r="W3">
-        <v>0.08799999999999999</v>
+        <v>0.3085714285714286</v>
       </c>
       <c r="X3">
-        <v>0.1141091819445309</v>
+        <v>0.09692740985282819</v>
       </c>
       <c r="Y3">
-        <v>-0.02610918194453091</v>
+        <v>0.2116440187186004</v>
       </c>
       <c r="Z3">
-        <v>1.838006230529595</v>
+        <v>12.66579973992198</v>
       </c>
       <c r="AA3">
-        <v>0.1012605968339888</v>
+        <v>0.7790303430440072</v>
       </c>
       <c r="AB3">
-        <v>0.1132675289537689</v>
+        <v>0.09647778500188005</v>
       </c>
       <c r="AC3">
-        <v>-0.01200693211978014</v>
+        <v>0.6825525580421271</v>
       </c>
       <c r="AD3">
-        <v>1.29</v>
+        <v>0.98</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.29</v>
+        <v>0.98</v>
       </c>
       <c r="AG3">
-        <v>-9.809999999999999</v>
+        <v>-7.619999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.02136115250869349</v>
+        <v>0.0121317157712305</v>
       </c>
       <c r="AI3">
-        <v>0.06865353911655137</v>
+        <v>0.0168732782369146</v>
       </c>
       <c r="AJ3">
-        <v>-0.1990261716372489</v>
+        <v>-0.1055694098088113</v>
       </c>
       <c r="AK3">
-        <v>-1.275682704811443</v>
+        <v>-0.1540016168148747</v>
       </c>
       <c r="AL3">
-        <v>0.03</v>
+        <v>0.043</v>
       </c>
       <c r="AM3">
-        <v>0.03</v>
+        <v>0.043</v>
       </c>
       <c r="AN3">
-        <v>0.2447817836812144</v>
+        <v>0.1121281464530892</v>
       </c>
       <c r="AO3">
-        <v>150.3333333333333</v>
+        <v>183.953488372093</v>
       </c>
       <c r="AP3">
-        <v>-1.861480075901328</v>
+        <v>-0.871853546910755</v>
       </c>
       <c r="AQ3">
-        <v>150.3333333333333</v>
+        <v>183.953488372093</v>
       </c>
     </row>
   </sheetData>
